--- a/xls/square_20_tri3_9.xlsx
+++ b/xls/square_20_tri3_9.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>441</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>64</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>294</v>
+      </c>
+      <c r="I7">
+        <v>31.319006184087257</v>
+      </c>
+      <c r="J7">
+        <v>31.397017060295745</v>
+      </c>
+      <c r="K7">
+        <v>13.643905518726854</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>441</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>81</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>384</v>
+      </c>
+      <c r="I8">
+        <v>5.173545895778925</v>
+      </c>
+      <c r="J8">
+        <v>3.699972536386357</v>
+      </c>
+      <c r="K8">
+        <v>1.6904728947557548</v>
+      </c>
+    </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>11</v>
